--- a/data/config/luban/config/general/title.xlsx
+++ b/data/config/luban/config/general/title.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Item" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Item!$A$3:$C$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Item!$A$3:$C$13</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1697,7 +1697,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A3:C12" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A3:C13" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="D3">
